--- a/Laporan Grade Induk/grade 19 september.xlsx
+++ b/Laporan Grade Induk/grade 19 september.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xenov\Downloads\cekbarkot\Laporan Grade Induk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53B3338F-EA26-4BB9-ADCB-3A3505486874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E7903E-088C-4FE1-B04F-FACA0F3C1E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,7 +883,7 @@
         <v>63</v>
       </c>
       <c r="D23" s="3">
-        <v>374179</v>
+        <v>374139</v>
       </c>
       <c r="E23" s="4">
         <v>41</v>
